--- a/VALIDATION/CAS SFS04/Cas SFS04.xlsx
+++ b/VALIDATION/CAS SFS04/Cas SFS04.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\RAID 1\LOGICIELS\CTICM AM - POUTRE MIXTE\DEV23\VALIDATION\CAS SFS04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BB310B3-63F5-4206-B698-70C73DA6C15A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C4020B4-00AC-4DFD-A6E0-DA2F54802E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1140" yWindow="1140" windowWidth="21600" windowHeight="13950" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -986,7 +986,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1227,9 +1227,6 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1573,7 +1570,7 @@
       </c>
       <c r="I6" s="90">
         <f>D56</f>
-        <v>10.631122242447166</v>
+        <v>11.121622242447165</v>
       </c>
       <c r="J6" t="s">
         <v>7</v>
@@ -1740,7 +1737,7 @@
       </c>
       <c r="J13" s="9">
         <f>qG*LL^2/8</f>
-        <v>107.64011270477755</v>
+        <v>112.60642520477755</v>
       </c>
       <c r="K13" s="12" t="s">
         <v>18</v>
@@ -1762,7 +1759,7 @@
       </c>
       <c r="J14" s="80">
         <f>qG*LL/2</f>
-        <v>47.840050091012245</v>
+        <v>50.047300091012239</v>
       </c>
       <c r="K14" s="15" t="s">
         <v>8</v>
@@ -2086,7 +2083,7 @@
       </c>
       <c r="J23" s="48">
         <f>GammaG*MEdG+GammaQ*(MEd_Q1+Psi_0*MEd_Q2)</f>
-        <v>449.06415215144966</v>
+        <v>455.76867402644973</v>
       </c>
       <c r="K23" s="31" t="s">
         <v>18</v>
@@ -2126,7 +2123,7 @@
       </c>
       <c r="J24" s="48">
         <f>GammaG*VEdG+GammaQ*(VEd_Q1+Psi_0*VEd_Q2)</f>
-        <v>199.58406762286654</v>
+        <v>202.56385512286653</v>
       </c>
       <c r="K24" s="34" t="s">
         <v>8</v>
@@ -2163,7 +2160,7 @@
       </c>
       <c r="J25" s="48">
         <f>GammaG*MEdG+GammaQ*(Psi_0*MEd_Q1+MEd_Q2)</f>
-        <v>357.93915215144966</v>
+        <v>364.64367402644973</v>
       </c>
       <c r="K25" s="37" t="s">
         <v>18</v>
@@ -2177,7 +2174,7 @@
       </c>
       <c r="J26" s="48">
         <f>GammaG*VEdG+GammaQ*(Psi_0*VEd_Q1+VEd_Q2)</f>
-        <v>159.08406762286651</v>
+        <v>162.06385512286653</v>
       </c>
       <c r="K26" s="40" t="s">
         <v>8</v>
@@ -2340,7 +2337,7 @@
       </c>
       <c r="J30" s="54">
         <f>GammaG*qG+GammaQ*(qQ_1)</f>
-        <v>44.352015027303679</v>
+        <v>45.01419002730367</v>
       </c>
       <c r="K30" t="s">
         <v>7</v>
@@ -2484,7 +2481,7 @@
       </c>
       <c r="J36" s="52">
         <f>MEd_U1/MplRdRed</f>
-        <v>0.5490953017454383</v>
+        <v>0.55731905121817715</v>
       </c>
       <c r="M36" s="41" t="s">
         <v>26</v>
@@ -2522,7 +2519,7 @@
       </c>
       <c r="J37" s="52">
         <f>VEd_U1/Q62</f>
-        <v>0.13583082590556392</v>
+        <v>0.13785877834670204</v>
       </c>
       <c r="M37" s="41" t="s">
         <v>91</v>
@@ -2661,7 +2658,7 @@
         <v>100</v>
       </c>
       <c r="D42" s="6">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="E42" t="s">
         <v>2</v>
@@ -2681,7 +2678,7 @@
       </c>
       <c r="D43" s="77">
         <f>td-hBac</f>
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E43" t="s">
         <v>2</v>
@@ -2781,7 +2778,7 @@
       </c>
       <c r="D50" s="47">
         <f>AVERAGE(D30:D31)*tc*(1+b0Bac*hBac/eBac/tc)/1000</f>
-        <v>0.37333333333333329</v>
+        <v>0.39333333333333337</v>
       </c>
       <c r="E50" t="s">
         <v>66</v>
@@ -2793,7 +2790,7 @@
       </c>
       <c r="D51" s="49">
         <f>Ac*rhoC</f>
-        <v>933.33333333333326</v>
+        <v>983.33333333333337</v>
       </c>
       <c r="E51" t="s">
         <v>63</v>
@@ -2819,7 +2816,7 @@
       </c>
       <c r="D52" s="80">
         <f>D51*9.81/1000</f>
-        <v>9.1560000000000006</v>
+        <v>9.6464999999999996</v>
       </c>
       <c r="E52" t="s">
         <v>7</v>
@@ -2882,7 +2879,7 @@
         <v>326.25</v>
       </c>
       <c r="P53" s="67">
-        <f>ABS(O53-zANP)</f>
+        <f t="shared" ref="P53:P58" si="8">ABS(O53-zANP)</f>
         <v>294.75</v>
       </c>
       <c r="Q53" s="69">
@@ -2925,7 +2922,7 @@
         <v>308.96906564846466</v>
       </c>
       <c r="P54" s="68">
-        <f>ABS(O54-zANP)</f>
+        <f t="shared" si="8"/>
         <v>277.46906564846466</v>
       </c>
       <c r="Q54" s="70">
@@ -2964,11 +2961,11 @@
         <v>173.25</v>
       </c>
       <c r="P55" s="68">
-        <f>ABS(O55-zANP)</f>
+        <f t="shared" si="8"/>
         <v>141.75</v>
       </c>
       <c r="Q55" s="70">
-        <f t="shared" ref="Q55:Q57" si="8">N55*P55/1000</f>
+        <f t="shared" ref="Q55:Q57" si="9">N55*P55/1000</f>
         <v>210.97715625000001</v>
       </c>
       <c r="R55" s="97"/>
@@ -2984,9 +2981,9 @@
       <c r="C56" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D56" s="100">
+      <c r="D56" s="99">
         <f>SUM(D52:D54)</f>
-        <v>10.631122242447166</v>
+        <v>11.121622242447165</v>
       </c>
       <c r="E56" s="57" t="s">
         <v>7</v>
@@ -3004,11 +3001,11 @@
         <v>15.749999999999996</v>
       </c>
       <c r="P56" s="68">
-        <f>ABS(O56-zANP)</f>
+        <f t="shared" si="8"/>
         <v>15.749999999999996</v>
       </c>
       <c r="Q56" s="70">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.6046562499999992</v>
       </c>
       <c r="R56" s="97"/>
@@ -3030,11 +3027,11 @@
         <v>6.0309343515353087</v>
       </c>
       <c r="P57" s="68">
-        <f>ABS(O57-zANP)</f>
+        <f t="shared" si="8"/>
         <v>25.469065648464685</v>
       </c>
       <c r="Q57" s="70">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3.3469811129787237</v>
       </c>
       <c r="R57" s="97"/>
@@ -3059,7 +3056,7 @@
         <v>-11.25</v>
       </c>
       <c r="P58" s="73">
-        <f>ABS(O58-zANP)</f>
+        <f t="shared" si="8"/>
         <v>42.749999999999993</v>
       </c>
       <c r="Q58" s="98">
@@ -3187,7 +3184,7 @@
       </c>
     </row>
     <row r="67" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="C67" s="99" t="s">
+      <c r="C67" s="3" t="s">
         <v>175</v>
       </c>
       <c r="D67" s="8">
@@ -3222,7 +3219,7 @@
       </c>
       <c r="N71" s="54">
         <f>5/384*qG*LL^4/(E*IncertieCM/100)*1000^2</f>
-        <v>13.38318563082437</v>
+        <v>14.000660663301119</v>
       </c>
       <c r="O71" t="s">
         <v>2</v>
@@ -3262,7 +3259,7 @@
       </c>
       <c r="N75" s="54">
         <f>N71+N72+Psi_0*N73</f>
-        <v>38.560556985635749</v>
+        <v>39.178032018112503</v>
       </c>
       <c r="O75" t="s">
         <v>2</v>
@@ -3298,7 +3295,7 @@
       </c>
       <c r="N80" s="56">
         <f>qG*LL/g*1000</f>
-        <v>9753.3231582084081</v>
+        <v>10203.323158208408</v>
       </c>
       <c r="O80" t="s">
         <v>65</v>
@@ -3330,7 +3327,7 @@
       </c>
       <c r="N83" s="56">
         <f>N80+N82*N81</f>
-        <v>13423.04792885061</v>
+        <v>13873.04792885061</v>
       </c>
       <c r="O83" t="s">
         <v>65</v>
@@ -3346,7 +3343,7 @@
       </c>
       <c r="N85" s="56">
         <f>N83/2</f>
-        <v>6711.5239644253052</v>
+        <v>6936.5239644253052</v>
       </c>
       <c r="O85" t="s">
         <v>65</v>
@@ -3362,7 +3359,7 @@
       </c>
       <c r="N87" s="54">
         <f>1/2/PI()*SQRT(PI()^4*(E*IncertieCM/100)/N83/LL^3)</f>
-        <v>4.1366117032520613</v>
+        <v>4.0689690214763425</v>
       </c>
       <c r="O87" t="s">
         <v>78</v>
@@ -3423,11 +3420,11 @@
       </c>
       <c r="F7" s="78">
         <f t="shared" ref="F7:F12" si="1">MEd_U1*E7*1000</f>
-        <v>-330.93150478808275</v>
+        <v>-335.87230779439824</v>
       </c>
       <c r="G7" s="93">
         <f t="shared" ref="G7:G12" si="2">ABS(F7/(FyS/GammaM0))</f>
-        <v>0.78793215425733987</v>
+        <v>0.79969597093904343</v>
       </c>
       <c r="I7" s="75"/>
       <c r="J7" s="4"/>
@@ -3449,11 +3446,11 @@
       </c>
       <c r="F8" s="78">
         <f t="shared" si="1"/>
-        <v>-299.664824513138</v>
+        <v>-304.13881639490103</v>
       </c>
       <c r="G8" s="93">
         <f t="shared" si="2"/>
-        <v>0.71348767741223329</v>
+        <v>0.72414003903547863</v>
       </c>
       <c r="K8">
         <v>-138.15</v>
@@ -3498,11 +3495,11 @@
       </c>
       <c r="F10" s="78">
         <f t="shared" si="1"/>
-        <v>138.06869933608891</v>
+        <v>140.13006319805987</v>
       </c>
       <c r="G10" s="93">
         <f t="shared" si="2"/>
-        <v>0.32873499841925929</v>
+        <v>0.33364300761442828</v>
       </c>
       <c r="K10">
         <f>InertieY_MM4</f>
@@ -3522,11 +3519,11 @@
       </c>
       <c r="F11" s="78">
         <f t="shared" si="1"/>
-        <v>169.33537961103372</v>
+        <v>171.86355459755706</v>
       </c>
       <c r="G11" s="93">
         <f t="shared" si="2"/>
-        <v>0.40317947526436598</v>
+        <v>0.40919893951799297</v>
       </c>
     </row>
     <row r="12" spans="3:11" x14ac:dyDescent="0.25">
@@ -3543,11 +3540,11 @@
       </c>
       <c r="F12" s="78">
         <f t="shared" si="1"/>
-        <v>169.33537961103372</v>
+        <v>171.86355459755706</v>
       </c>
       <c r="G12" s="93">
         <f t="shared" si="2"/>
-        <v>0.40317947526436598</v>
+        <v>0.40919893951799297</v>
       </c>
     </row>
     <row r="13" spans="3:11" x14ac:dyDescent="0.25">
@@ -3587,7 +3584,7 @@
       </c>
       <c r="Q18" s="5">
         <f>Feuil1!P38*PsiY</f>
-        <v>1635.0588998588348</v>
+        <v>1634.7687896068117</v>
       </c>
     </row>
     <row r="19" spans="3:21" x14ac:dyDescent="0.25">
@@ -3630,7 +3627,7 @@
       </c>
       <c r="D21" s="80">
         <f>qELU*df*6/tf^2/2</f>
-        <v>30.685023730001213</v>
+        <v>31.143150730001206</v>
       </c>
       <c r="E21" t="s">
         <v>43</v>
@@ -3652,7 +3649,7 @@
       </c>
       <c r="L21" s="80">
         <f>qELU/2</f>
-        <v>22.17600751365184</v>
+        <v>22.507095013651835</v>
       </c>
       <c r="M21" t="s">
         <v>7</v>
@@ -3662,7 +3659,7 @@
       </c>
       <c r="Q21" s="52">
         <f>0.5+(Q26-Q31)/2/Q18</f>
-        <v>9.5427418512500362E-2</v>
+        <v>9.5355622027074871E-2</v>
       </c>
     </row>
     <row r="22" spans="3:21" x14ac:dyDescent="0.25">
@@ -3692,7 +3689,7 @@
       </c>
       <c r="L23" s="80">
         <f>qEdFl*(dbt/1000)</f>
-        <v>1.849848626763791</v>
+        <v>1.8774668423887906</v>
       </c>
       <c r="M23" t="s">
         <v>154</v>
@@ -3731,22 +3728,22 @@
       </c>
       <c r="D25" s="59">
         <f>F10</f>
-        <v>138.06869933608891</v>
+        <v>140.13006319805987</v>
       </c>
       <c r="E25" s="66">
         <f>+D21</f>
-        <v>30.685023730001213</v>
+        <v>31.143150730001206</v>
       </c>
       <c r="F25" s="4">
         <v>0</v>
       </c>
       <c r="G25" s="78">
         <f>SQRT(D25^2+E25^2-D25*E25+3*F25^2)</f>
-        <v>125.57027953370083</v>
+        <v>127.44504215269441</v>
       </c>
       <c r="H25" s="94">
         <f t="shared" ref="H25:H30" si="3">G25/(FyS/GammaM0)</f>
-        <v>0.29897685603262103</v>
+        <v>0.30344057655403434</v>
       </c>
       <c r="K25" s="3"/>
       <c r="Q25" s="5" t="s">
@@ -3768,29 +3765,29 @@
       </c>
       <c r="D26" s="59">
         <f>AVERAGE(D25,D27)</f>
-        <v>153.70203947356131</v>
+        <v>155.99680889780848</v>
       </c>
       <c r="E26" s="4">
         <v>0</v>
       </c>
       <c r="F26" s="75">
         <f>3/2*qELU/tf/2</f>
-        <v>1.4784005009101227</v>
+        <v>1.5004730009101224</v>
       </c>
       <c r="G26" s="78">
         <f t="shared" ref="G26:G30" si="4">SQRT(D26^2+E26^2-D26*E26+3*F26^2)</f>
-        <v>153.72336823806418</v>
+        <v>156.01845610048434</v>
       </c>
       <c r="H26" s="94">
         <f t="shared" si="3"/>
-        <v>0.36600801961443852</v>
+        <v>0.37147251452496272</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>155</v>
       </c>
       <c r="L26" s="47">
         <f>(L23/L24)</f>
-        <v>4.3500261652293738E-2</v>
+        <v>4.4149719985627056E-2</v>
       </c>
       <c r="P26" s="41" t="s">
         <v>161</v>
@@ -3819,22 +3816,22 @@
       </c>
       <c r="D27" s="59">
         <f>F11</f>
-        <v>169.33537961103372</v>
+        <v>171.86355459755706</v>
       </c>
       <c r="E27" s="66">
         <f>-E25</f>
-        <v>-30.685023730001213</v>
+        <v>-31.143150730001206</v>
       </c>
       <c r="F27" s="4">
         <v>0</v>
       </c>
       <c r="G27" s="78">
         <f t="shared" si="4"/>
-        <v>186.58001396456419</v>
+        <v>189.36565111477995</v>
       </c>
       <c r="H27" s="94">
         <f t="shared" si="3"/>
-        <v>0.44423812848705757</v>
+        <v>0.45087059789233319</v>
       </c>
       <c r="K27" s="3"/>
       <c r="P27" s="41" t="s">
@@ -3864,7 +3861,7 @@
       </c>
       <c r="D28" s="59">
         <f>F11</f>
-        <v>169.33537961103372</v>
+        <v>171.86355459755706</v>
       </c>
       <c r="E28" s="66" t="e">
         <f>#REF!</f>
@@ -3886,26 +3883,26 @@
       </c>
       <c r="L28" s="47">
         <f>(RatioFi-SQRT(RatioFi^2-16*RatioFi+16))/2/(RatioFi-2)</f>
-        <v>0.98869774745810113</v>
+        <v>0.98852232175770927</v>
       </c>
       <c r="P28" s="41" t="s">
         <v>163</v>
       </c>
       <c r="Q28" s="82">
         <f>(1-Q21)*Q18</f>
-        <v>1479.0294499294173</v>
+        <v>1478.8843948034059</v>
       </c>
       <c r="R28" s="85">
         <f>hw-(1-Q21)*hw/2</f>
-        <v>172.52981841571881</v>
+        <v>172.51851046926427</v>
       </c>
       <c r="S28" s="68">
         <f t="shared" ref="S28:S30" si="5">ABS(R28-$Q$22)</f>
-        <v>141.02981841571881</v>
+        <v>141.01851046926427</v>
       </c>
       <c r="T28" s="70">
         <f t="shared" ref="T28:T30" si="6">Q28*S28/1000</f>
-        <v>208.58725475504619</v>
+        <v>208.55007451141566</v>
       </c>
       <c r="U28" s="97"/>
     </row>
@@ -3915,7 +3912,7 @@
       </c>
       <c r="D29" s="59">
         <f>AVERAGE(D28,D30)</f>
-        <v>169.33537961103372</v>
+        <v>171.86355459755706</v>
       </c>
       <c r="E29" s="4">
         <v>0</v>
@@ -3938,19 +3935,19 @@
       </c>
       <c r="Q29" s="82">
         <f>Q21*Q18</f>
-        <v>156.02944992941744</v>
+        <v>155.88439480340583</v>
       </c>
       <c r="R29" s="85">
         <f>Q21*hw/2</f>
-        <v>15.029818415718808</v>
+        <v>15.018510469264292</v>
       </c>
       <c r="S29" s="68">
         <f t="shared" si="5"/>
-        <v>16.470181584281185</v>
+        <v>16.481489530735701</v>
       </c>
       <c r="T29" s="70">
         <f t="shared" si="6"/>
-        <v>2.5698333728330143</v>
+        <v>2.5692070209574038</v>
       </c>
       <c r="U29" s="97"/>
     </row>
@@ -3960,7 +3957,7 @@
       </c>
       <c r="D30" s="59">
         <f>F12</f>
-        <v>169.33537961103372</v>
+        <v>171.86355459755706</v>
       </c>
       <c r="E30" s="66" t="e">
         <f>-E28</f>
@@ -4023,7 +4020,7 @@
     <row r="32" spans="3:21" x14ac:dyDescent="0.25">
       <c r="T32" s="83">
         <f>SUM(T26:T31)</f>
-        <v>817.82552268064512</v>
+        <v>817.78771608513898</v>
       </c>
       <c r="U32" t="s">
         <v>18</v>
@@ -4035,7 +4032,7 @@
       </c>
       <c r="T34" s="76">
         <f>T32</f>
-        <v>817.82552268064512</v>
+        <v>817.78771608513898</v>
       </c>
       <c r="U34" t="s">
         <v>18</v>
@@ -4047,7 +4044,7 @@
       </c>
       <c r="Q36" s="55">
         <f>SUM(Q26:Q28)</f>
-        <v>3122.4430305913556</v>
+        <v>3122.2979754653443</v>
       </c>
     </row>
     <row r="37" spans="16:21" x14ac:dyDescent="0.25">
@@ -4056,7 +4053,7 @@
       </c>
       <c r="Q37" s="55">
         <f>SUM(Q29:Q31)</f>
-        <v>3122.4430305913561</v>
+        <v>3122.2979754653443</v>
       </c>
     </row>
   </sheetData>
